--- a/Pruebas calificadas/COLEGIO BICENTENARIO DE LA INDEPENDENCIA IED DIAGNOSTICA 1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO BICENTENARIO DE LA INDEPENDENCIA IED DIAGNOSTICA 1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1811,11 +1795,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1823,7 +1803,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2052,11 +2032,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2064,7 +2040,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2305,11 +2281,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2317,7 +2289,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2558,11 +2530,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2570,7 +2538,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2811,11 +2779,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2823,7 +2787,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3064,11 +3028,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3076,7 +3036,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3317,11 +3277,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3329,7 +3285,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3570,11 +3526,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3582,7 +3534,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3823,11 +3775,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3835,7 +3783,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4076,11 +4024,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4088,7 +4032,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4329,11 +4273,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4341,7 +4281,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4582,11 +4522,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4594,7 +4530,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4835,11 +4771,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4847,7 +4779,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5088,11 +5020,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5100,7 +5028,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5341,11 +5269,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5353,7 +5277,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5594,11 +5518,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5606,7 +5526,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5847,11 +5767,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5859,7 +5775,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6100,11 +6016,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6112,7 +6024,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6353,11 +6265,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6365,7 +6273,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6602,11 +6510,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6614,7 +6518,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6855,11 +6759,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6867,7 +6767,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7108,11 +7008,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7120,7 +7016,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7361,11 +7257,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7373,7 +7265,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7614,11 +7506,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7626,7 +7514,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7867,11 +7755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7879,7 +7763,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8120,11 +8004,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8132,7 +8012,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8373,11 +8253,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8385,7 +8261,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8626,11 +8502,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8638,7 +8510,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8879,11 +8751,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8891,7 +8759,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9132,11 +9000,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9144,7 +9008,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9385,11 +9249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9397,7 +9257,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9650,7 +9506,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9903,7 +9755,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10144,11 +9996,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10156,7 +10004,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10397,11 +10245,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10409,7 +10253,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10650,11 +10494,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10662,7 +10502,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10903,11 +10743,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10915,7 +10751,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11156,11 +10992,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11168,7 +11000,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11409,11 +11241,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11421,7 +11249,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11658,11 +11486,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11670,7 +11494,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11911,11 +11735,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11923,7 +11743,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12164,11 +11984,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12176,7 +11992,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12417,11 +12233,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12429,7 +12241,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12670,11 +12482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12682,7 +12490,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12923,11 +12731,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12935,7 +12739,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13172,11 +12976,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13184,7 +12984,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13425,11 +13225,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13437,7 +13233,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13678,11 +13474,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13690,7 +13482,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13931,11 +13723,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13943,7 +13731,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14184,11 +13972,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -14196,7 +13980,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14437,11 +14221,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -14449,7 +14229,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14690,11 +14470,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -14702,7 +14478,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14943,11 +14719,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -14955,7 +14727,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15196,11 +14968,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -15208,7 +14976,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15449,11 +15217,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -15461,7 +15225,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15702,11 +15466,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -15714,7 +15474,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED)</t>
+          <t>COLEGIO BICENTENARIO DE LA INDEPENDENCIA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
